--- a/esyluban/examples/release/DataTables/item/道具系统表.xlsx
+++ b/esyluban/examples/release/DataTables/item/道具系统表.xlsx
@@ -3735,7 +3735,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="R2:S2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="D4:D15 D18:D21 H4:H15 H18:H21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
